--- a/Data/portfolio_UPHES.xlsx
+++ b/Data/portfolio_UPHES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ericsson\Desktop\UPHES\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\DFL-for-UPHES\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543925E0-5DAE-45DB-9BDB-EA15260FCC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E353237-6D88-4275-A7E3-474BF4F95554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1128" yWindow="1572" windowWidth="16440" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32980" yWindow="980" windowWidth="28800" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>Normal water level of upper resevoir</t>
   </si>
   <si>
-    <t>half-full level of upper resevoir</t>
-  </si>
-  <si>
     <t>half-full level of lower resevoir</t>
   </si>
   <si>
@@ -195,19 +192,23 @@
   <si>
     <t>target volume at the end of the day(up)</t>
   </si>
+  <si>
+    <t>half-full level of upper resevoir</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -222,6 +223,13 @@
       <color rgb="FFFF0000"/>
       <name val="Hack"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -295,7 +303,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -304,8 +312,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -658,18 +666,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="52.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
-    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="37.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.53125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.86328125" style="2"/>
+    <col min="6" max="6" width="9.1328125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.86328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,7 +688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -689,7 +697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -700,7 +708,7 @@
         <v>294000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -711,9 +719,9 @@
         <v>294000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>6</v>
@@ -722,7 +730,7 @@
         <v>138180</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -733,7 +741,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -744,7 +752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -755,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -766,7 +774,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -777,7 +785,7 @@
         <v>0.93700000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
@@ -788,7 +796,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -801,7 +809,7 @@
       </c>
       <c r="F12"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
@@ -812,7 +820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
@@ -823,7 +831,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -834,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
@@ -853,7 +861,7 @@
         <v>365906.69855701132</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -864,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -876,10 +884,10 @@
         <v>588000</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
@@ -894,7 +902,7 @@
         <v>58.779987115799145</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
@@ -905,7 +913,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -916,9 +924,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>31</v>
@@ -928,18 +936,18 @@
         <v>10854.475576478206</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C23" s="12">
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -951,7 +959,7 @@
         <v>72.393719530024114</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -964,9 +972,9 @@
       </c>
       <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
@@ -976,7 +984,7 @@
       </c>
       <c r="D26" s="10"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -984,23 +992,23 @@
         <v>30</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="C28" s="12">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>19</v>
@@ -1011,9 +1019,9 @@
       </c>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>19</v>
@@ -1023,9 +1031,9 @@
       </c>
       <c r="D30" s="10"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>19</v>
@@ -1035,9 +1043,9 @@
         <v>22.393719530024111</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>19</v>
@@ -1047,12 +1055,13 @@
         <v>11.196859765012055</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" ht="171">
       <c r="A35" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
